--- a/ЦКП. РиЭ.xlsx
+++ b/ЦКП. РиЭ.xlsx
@@ -316,7 +316,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -394,6 +394,8 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1288,24 +1290,16 @@
       <c r="K37" s="34" t="n"/>
     </row>
     <row r="38" ht="45" customHeight="1">
-      <c r="B38" s="19" t="inlineStr">
-        <is>
-          <t>Примечание</t>
-        </is>
-      </c>
-      <c r="C38" s="38" t="inlineStr">
-        <is>
-          <t>Факт янв–авг не заполнен: отсутствует файл «аналитика группы продаж». Нормативы РиЭ — из схемы «Показатели»: выработка старшие ≥350 тыс. / менеджеры ≥215 тыс.; ср.чек ≥35 тыс.; ФОТ ≤32% МД; конверсия лид→оплата ≥5%.</t>
-        </is>
-      </c>
-      <c r="D38" s="35" t="n"/>
-      <c r="E38" s="35" t="n"/>
-      <c r="F38" s="35" t="n"/>
-      <c r="G38" s="35" t="n"/>
-      <c r="H38" s="35" t="n"/>
-      <c r="I38" s="35" t="n"/>
-      <c r="J38" s="35" t="n"/>
-      <c r="K38" s="36" t="n"/>
+      <c r="B38" s="39" t="n"/>
+      <c r="C38" s="39" t="n"/>
+      <c r="D38" s="40" t="n"/>
+      <c r="E38" s="40" t="n"/>
+      <c r="F38" s="40" t="n"/>
+      <c r="G38" s="40" t="n"/>
+      <c r="H38" s="40" t="n"/>
+      <c r="I38" s="40" t="n"/>
+      <c r="J38" s="40" t="n"/>
+      <c r="K38" s="40" t="n"/>
     </row>
     <row r="39" ht="12.75" customHeight="1">
       <c r="B39" s="19" t="n"/>
@@ -2311,9 +2305,6 @@
       <c r="K105" s="19" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="C38:K38"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/ЦКП. РиЭ.xlsx
+++ b/ЦКП. РиЭ.xlsx
@@ -316,7 +316,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -396,6 +396,12 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="19" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -855,7 +861,8 @@
       </c>
       <c r="E11" s="31" t="inlineStr">
         <is>
-          <t>— Выполнение личного плана по новым клиентам, ДДС и МД (минимум / норма / целевой)
+          <t>— План МД ≥ 350 тыс. руб./мес. (минимум/норма/целевой по периоду)
+— Новые клиенты, ДДС — по плану периода
 — Скорость реакции на лид — по регламенту</t>
         </is>
       </c>
@@ -902,7 +909,8 @@
       </c>
       <c r="E12" s="31" t="inlineStr">
         <is>
-          <t>— Выполнение личного плана по новым клиентам, ДДС и МД (минимум / норма / целевой)
+          <t>— План МД ≥ 320 тыс. руб./мес. (минимум/норма/целевой по периоду)
+— Новые клиенты, ДДС — по плану периода
 — Скорость реакции на лид — по регламенту</t>
         </is>
       </c>
@@ -949,7 +957,8 @@
       </c>
       <c r="E13" s="31" t="inlineStr">
         <is>
-          <t>— Выполнение личного плана грейда по новым клиентам, ДДС и МД (минимум / норма / целевой)
+          <t>— План МД 50–150 тыс. руб./мес. (по грейду младшего менеджера)
+— Новые клиенты, ДДС — по плану периода
 — Скорость реакции на лид — по регламенту</t>
         </is>
       </c>
@@ -962,7 +971,7 @@
       </c>
       <c r="G13" s="31" t="inlineStr">
         <is>
-          <t>— Выработка — по плану грейда младшего менеджера (ниже норматива менеджера 215 тыс. руб.)
+          <t>— Выработка / план МД грейда: 50–150 тыс. руб. (по аналитике группы)
 — Средний чек комплексных продаж ≥ 35 тыс. руб.
 — Конверсия лид → оплата ≥ 5%</t>
         </is>
@@ -1105,7 +1114,7 @@
       </c>
       <c r="C30" s="22" t="inlineStr">
         <is>
-          <t>Выручка, руб.</t>
+          <t>Выручка, руб. (в аналитике группы — нет помесячной выручки; заполнен МД ниже)</t>
         </is>
       </c>
       <c r="D30" s="21" t="n"/>
@@ -1180,14 +1189,14 @@
           <t>Савинская Евгения</t>
         </is>
       </c>
-      <c r="D32" s="33" t="n"/>
-      <c r="E32" s="33" t="n"/>
-      <c r="F32" s="33" t="n"/>
-      <c r="G32" s="33" t="n"/>
-      <c r="H32" s="33" t="n"/>
-      <c r="I32" s="33" t="n"/>
-      <c r="J32" s="33" t="n"/>
-      <c r="K32" s="33" t="n"/>
+      <c r="D32" s="41" t="n"/>
+      <c r="E32" s="41" t="n"/>
+      <c r="F32" s="41" t="n"/>
+      <c r="G32" s="41" t="n"/>
+      <c r="H32" s="41" t="n"/>
+      <c r="I32" s="41" t="n"/>
+      <c r="J32" s="41" t="n"/>
+      <c r="K32" s="41" t="n"/>
     </row>
     <row r="33">
       <c r="B33" s="32" t="inlineStr">
@@ -1200,14 +1209,14 @@
           <t>Багланова Антонина</t>
         </is>
       </c>
-      <c r="D33" s="34" t="n"/>
-      <c r="E33" s="34" t="n"/>
-      <c r="F33" s="34" t="n"/>
-      <c r="G33" s="34" t="n"/>
-      <c r="H33" s="34" t="n"/>
-      <c r="I33" s="34" t="n"/>
-      <c r="J33" s="34" t="n"/>
-      <c r="K33" s="34" t="n"/>
+      <c r="D33" s="41" t="n"/>
+      <c r="E33" s="41" t="n"/>
+      <c r="F33" s="41" t="n"/>
+      <c r="G33" s="41" t="n"/>
+      <c r="H33" s="41" t="n"/>
+      <c r="I33" s="41" t="n"/>
+      <c r="J33" s="41" t="n"/>
+      <c r="K33" s="41" t="n"/>
     </row>
     <row r="34">
       <c r="B34" s="32" t="inlineStr">
@@ -1220,14 +1229,14 @@
           <t>Соболев Максим</t>
         </is>
       </c>
-      <c r="D34" s="34" t="n"/>
-      <c r="E34" s="34" t="n"/>
-      <c r="F34" s="34" t="n"/>
-      <c r="G34" s="34" t="n"/>
-      <c r="H34" s="34" t="n"/>
-      <c r="I34" s="34" t="n"/>
-      <c r="J34" s="34" t="n"/>
-      <c r="K34" s="34" t="n"/>
+      <c r="D34" s="41" t="n"/>
+      <c r="E34" s="41" t="n"/>
+      <c r="F34" s="41" t="n"/>
+      <c r="G34" s="41" t="n"/>
+      <c r="H34" s="41" t="n"/>
+      <c r="I34" s="41" t="n"/>
+      <c r="J34" s="41" t="n"/>
+      <c r="K34" s="41" t="n"/>
     </row>
     <row r="35" ht="12.75" customHeight="1">
       <c r="B35" s="32" t="inlineStr">
@@ -1240,14 +1249,14 @@
           <t>Россинский Вадим</t>
         </is>
       </c>
-      <c r="D35" s="34" t="n"/>
-      <c r="E35" s="34" t="n"/>
-      <c r="F35" s="34" t="n"/>
-      <c r="G35" s="34" t="n"/>
-      <c r="H35" s="34" t="n"/>
-      <c r="I35" s="34" t="n"/>
-      <c r="J35" s="34" t="n"/>
-      <c r="K35" s="34" t="n"/>
+      <c r="D35" s="41" t="n"/>
+      <c r="E35" s="41" t="n"/>
+      <c r="F35" s="41" t="n"/>
+      <c r="G35" s="41" t="n"/>
+      <c r="H35" s="41" t="n"/>
+      <c r="I35" s="41" t="n"/>
+      <c r="J35" s="41" t="n"/>
+      <c r="K35" s="41" t="n"/>
     </row>
     <row r="36" ht="12.75" customHeight="1">
       <c r="B36" s="32" t="inlineStr">
@@ -1260,14 +1269,14 @@
           <t>Федосеев Максим</t>
         </is>
       </c>
-      <c r="D36" s="34" t="n"/>
-      <c r="E36" s="34" t="n"/>
-      <c r="F36" s="34" t="n"/>
-      <c r="G36" s="34" t="n"/>
-      <c r="H36" s="34" t="n"/>
-      <c r="I36" s="34" t="n"/>
-      <c r="J36" s="34" t="n"/>
-      <c r="K36" s="34" t="n"/>
+      <c r="D36" s="41" t="n"/>
+      <c r="E36" s="41" t="n"/>
+      <c r="F36" s="41" t="n"/>
+      <c r="G36" s="41" t="n"/>
+      <c r="H36" s="41" t="n"/>
+      <c r="I36" s="41" t="n"/>
+      <c r="J36" s="41" t="n"/>
+      <c r="K36" s="41" t="n"/>
     </row>
     <row r="37" ht="12.75" customHeight="1">
       <c r="B37" s="32" t="inlineStr">
@@ -1280,14 +1289,14 @@
           <t>Фёдорова Анастасия</t>
         </is>
       </c>
-      <c r="D37" s="34" t="n"/>
-      <c r="E37" s="34" t="n"/>
-      <c r="F37" s="34" t="n"/>
-      <c r="G37" s="34" t="n"/>
-      <c r="H37" s="34" t="n"/>
-      <c r="I37" s="34" t="n"/>
-      <c r="J37" s="34" t="n"/>
-      <c r="K37" s="34" t="n"/>
+      <c r="D37" s="41" t="n"/>
+      <c r="E37" s="41" t="n"/>
+      <c r="F37" s="41" t="n"/>
+      <c r="G37" s="41" t="n"/>
+      <c r="H37" s="41" t="n"/>
+      <c r="I37" s="41" t="n"/>
+      <c r="J37" s="41" t="n"/>
+      <c r="K37" s="41" t="n"/>
     </row>
     <row r="38" ht="45" customHeight="1">
       <c r="B38" s="39" t="n"/>
@@ -1480,14 +1489,30 @@
           <t>Савинская Евгения</t>
         </is>
       </c>
-      <c r="D51" s="33" t="n"/>
-      <c r="E51" s="33" t="n"/>
-      <c r="F51" s="33" t="n"/>
-      <c r="G51" s="33" t="n"/>
-      <c r="H51" s="33" t="n"/>
-      <c r="I51" s="33" t="n"/>
-      <c r="J51" s="33" t="n"/>
-      <c r="K51" s="33" t="n"/>
+      <c r="D51" s="41" t="n">
+        <v>983203</v>
+      </c>
+      <c r="E51" s="41" t="n">
+        <v>955437</v>
+      </c>
+      <c r="F51" s="41" t="n">
+        <v>796439</v>
+      </c>
+      <c r="G51" s="41" t="n">
+        <v>594768</v>
+      </c>
+      <c r="H51" s="41" t="n">
+        <v>1003911</v>
+      </c>
+      <c r="I51" s="41" t="n">
+        <v>1168363</v>
+      </c>
+      <c r="J51" s="41" t="n">
+        <v>1766374</v>
+      </c>
+      <c r="K51" s="41" t="n">
+        <v>1051883</v>
+      </c>
     </row>
     <row r="52" ht="12.75" customHeight="1">
       <c r="B52" s="32" t="inlineStr">
@@ -1500,14 +1525,30 @@
           <t>Багланова Антонина</t>
         </is>
       </c>
-      <c r="D52" s="34" t="n"/>
-      <c r="E52" s="34" t="n"/>
-      <c r="F52" s="34" t="n"/>
-      <c r="G52" s="34" t="n"/>
-      <c r="H52" s="34" t="n"/>
-      <c r="I52" s="34" t="n"/>
-      <c r="J52" s="34" t="n"/>
-      <c r="K52" s="34" t="n"/>
+      <c r="D52" s="41" t="n">
+        <v>156374</v>
+      </c>
+      <c r="E52" s="41" t="n">
+        <v>129868</v>
+      </c>
+      <c r="F52" s="41" t="n">
+        <v>88587</v>
+      </c>
+      <c r="G52" s="41" t="n">
+        <v>89000</v>
+      </c>
+      <c r="H52" s="41" t="n">
+        <v>127625</v>
+      </c>
+      <c r="I52" s="41" t="n">
+        <v>147020</v>
+      </c>
+      <c r="J52" s="41" t="n">
+        <v>171961</v>
+      </c>
+      <c r="K52" s="41" t="n">
+        <v>86517</v>
+      </c>
     </row>
     <row r="53" ht="12.75" customHeight="1">
       <c r="B53" s="32" t="inlineStr">
@@ -1520,14 +1561,30 @@
           <t>Соболев Максим</t>
         </is>
       </c>
-      <c r="D53" s="34" t="n"/>
-      <c r="E53" s="34" t="n"/>
-      <c r="F53" s="34" t="n"/>
-      <c r="G53" s="34" t="n"/>
-      <c r="H53" s="34" t="n"/>
-      <c r="I53" s="34" t="n"/>
-      <c r="J53" s="34" t="n"/>
-      <c r="K53" s="34" t="n"/>
+      <c r="D53" s="41" t="n">
+        <v>437270</v>
+      </c>
+      <c r="E53" s="41" t="n">
+        <v>336283</v>
+      </c>
+      <c r="F53" s="41" t="n">
+        <v>438973</v>
+      </c>
+      <c r="G53" s="41" t="n">
+        <v>160000</v>
+      </c>
+      <c r="H53" s="41" t="n">
+        <v>262000</v>
+      </c>
+      <c r="I53" s="41" t="n">
+        <v>466583</v>
+      </c>
+      <c r="J53" s="41" t="n">
+        <v>375589</v>
+      </c>
+      <c r="K53" s="41" t="n">
+        <v>202857</v>
+      </c>
     </row>
     <row r="54" ht="12.75" customHeight="1">
       <c r="B54" s="32" t="inlineStr">
@@ -1540,14 +1597,30 @@
           <t>Россинский Вадим</t>
         </is>
       </c>
-      <c r="D54" s="34" t="n"/>
-      <c r="E54" s="34" t="n"/>
-      <c r="F54" s="34" t="n"/>
-      <c r="G54" s="34" t="n"/>
-      <c r="H54" s="34" t="n"/>
-      <c r="I54" s="34" t="n"/>
-      <c r="J54" s="34" t="n"/>
-      <c r="K54" s="34" t="n"/>
+      <c r="D54" s="41" t="n">
+        <v>245527</v>
+      </c>
+      <c r="E54" s="41" t="n">
+        <v>343570</v>
+      </c>
+      <c r="F54" s="41" t="n">
+        <v>176445</v>
+      </c>
+      <c r="G54" s="41" t="n">
+        <v>202082</v>
+      </c>
+      <c r="H54" s="41" t="n">
+        <v>424127</v>
+      </c>
+      <c r="I54" s="41" t="n">
+        <v>334011</v>
+      </c>
+      <c r="J54" s="41" t="n">
+        <v>342643</v>
+      </c>
+      <c r="K54" s="41" t="n">
+        <v>334237</v>
+      </c>
     </row>
     <row r="55" ht="12.75" customHeight="1">
       <c r="B55" s="32" t="inlineStr">
@@ -1560,14 +1633,30 @@
           <t>Федосеев Максим</t>
         </is>
       </c>
-      <c r="D55" s="34" t="n"/>
-      <c r="E55" s="34" t="n"/>
-      <c r="F55" s="34" t="n"/>
-      <c r="G55" s="34" t="n"/>
-      <c r="H55" s="34" t="n"/>
-      <c r="I55" s="34" t="n"/>
-      <c r="J55" s="34" t="n"/>
-      <c r="K55" s="34" t="n"/>
+      <c r="D55" s="41" t="n">
+        <v>144032</v>
+      </c>
+      <c r="E55" s="41" t="n">
+        <v>145716</v>
+      </c>
+      <c r="F55" s="41" t="n">
+        <v>92434</v>
+      </c>
+      <c r="G55" s="41" t="n">
+        <v>143686</v>
+      </c>
+      <c r="H55" s="41" t="n">
+        <v>190159</v>
+      </c>
+      <c r="I55" s="41" t="n">
+        <v>220749</v>
+      </c>
+      <c r="J55" s="41" t="n">
+        <v>775616</v>
+      </c>
+      <c r="K55" s="41" t="n">
+        <v>272821</v>
+      </c>
     </row>
     <row r="56" ht="12.75" customHeight="1">
       <c r="B56" s="32" t="inlineStr">
@@ -1580,14 +1669,18 @@
           <t>Фёдорова Анастасия</t>
         </is>
       </c>
-      <c r="D56" s="34" t="n"/>
-      <c r="E56" s="34" t="n"/>
-      <c r="F56" s="34" t="n"/>
-      <c r="G56" s="34" t="n"/>
-      <c r="H56" s="34" t="n"/>
-      <c r="I56" s="34" t="n"/>
-      <c r="J56" s="34" t="n"/>
-      <c r="K56" s="34" t="n"/>
+      <c r="D56" s="41" t="n"/>
+      <c r="E56" s="41" t="n"/>
+      <c r="F56" s="41" t="n"/>
+      <c r="G56" s="41" t="n"/>
+      <c r="H56" s="41" t="n"/>
+      <c r="I56" s="41" t="n"/>
+      <c r="J56" s="41" t="n">
+        <v>100565</v>
+      </c>
+      <c r="K56" s="41" t="n">
+        <v>155451</v>
+      </c>
     </row>
     <row r="57" ht="12.75" customHeight="1">
       <c r="B57" s="19" t="n"/>
@@ -1787,14 +1880,30 @@
           <t>Савинская Евгения</t>
         </is>
       </c>
-      <c r="D72" s="33" t="n"/>
-      <c r="E72" s="33" t="n"/>
-      <c r="F72" s="33" t="n"/>
-      <c r="G72" s="33" t="n"/>
-      <c r="H72" s="33" t="n"/>
-      <c r="I72" s="33" t="n"/>
-      <c r="J72" s="33" t="n"/>
-      <c r="K72" s="33" t="n"/>
+      <c r="D72" s="41" t="n">
+        <v>983203</v>
+      </c>
+      <c r="E72" s="41" t="n">
+        <v>955437</v>
+      </c>
+      <c r="F72" s="41" t="n">
+        <v>796439</v>
+      </c>
+      <c r="G72" s="41" t="n">
+        <v>594768</v>
+      </c>
+      <c r="H72" s="41" t="n">
+        <v>1003911</v>
+      </c>
+      <c r="I72" s="41" t="n">
+        <v>1168363</v>
+      </c>
+      <c r="J72" s="41" t="n">
+        <v>1766374</v>
+      </c>
+      <c r="K72" s="41" t="n">
+        <v>1051883</v>
+      </c>
     </row>
     <row r="73" ht="12.75" customHeight="1">
       <c r="B73" s="32" t="inlineStr">
@@ -1807,14 +1916,30 @@
           <t>Багланова Антонина</t>
         </is>
       </c>
-      <c r="D73" s="34" t="n"/>
-      <c r="E73" s="34" t="n"/>
-      <c r="F73" s="34" t="n"/>
-      <c r="G73" s="34" t="n"/>
-      <c r="H73" s="34" t="n"/>
-      <c r="I73" s="34" t="n"/>
-      <c r="J73" s="34" t="n"/>
-      <c r="K73" s="34" t="n"/>
+      <c r="D73" s="41" t="n">
+        <v>156374</v>
+      </c>
+      <c r="E73" s="41" t="n">
+        <v>129868</v>
+      </c>
+      <c r="F73" s="41" t="n">
+        <v>88587</v>
+      </c>
+      <c r="G73" s="41" t="n">
+        <v>89000</v>
+      </c>
+      <c r="H73" s="41" t="n">
+        <v>127625</v>
+      </c>
+      <c r="I73" s="41" t="n">
+        <v>147020</v>
+      </c>
+      <c r="J73" s="41" t="n">
+        <v>171961</v>
+      </c>
+      <c r="K73" s="41" t="n">
+        <v>86517</v>
+      </c>
     </row>
     <row r="74" ht="12.75" customHeight="1">
       <c r="B74" s="32" t="inlineStr">
@@ -1827,14 +1952,30 @@
           <t>Соболев Максим</t>
         </is>
       </c>
-      <c r="D74" s="34" t="n"/>
-      <c r="E74" s="34" t="n"/>
-      <c r="F74" s="34" t="n"/>
-      <c r="G74" s="34" t="n"/>
-      <c r="H74" s="34" t="n"/>
-      <c r="I74" s="34" t="n"/>
-      <c r="J74" s="34" t="n"/>
-      <c r="K74" s="34" t="n"/>
+      <c r="D74" s="41" t="n">
+        <v>437270</v>
+      </c>
+      <c r="E74" s="41" t="n">
+        <v>336283</v>
+      </c>
+      <c r="F74" s="41" t="n">
+        <v>438973</v>
+      </c>
+      <c r="G74" s="41" t="n">
+        <v>160000</v>
+      </c>
+      <c r="H74" s="41" t="n">
+        <v>262000</v>
+      </c>
+      <c r="I74" s="41" t="n">
+        <v>466583</v>
+      </c>
+      <c r="J74" s="41" t="n">
+        <v>375589</v>
+      </c>
+      <c r="K74" s="41" t="n">
+        <v>202857</v>
+      </c>
     </row>
     <row r="75" ht="12.75" customHeight="1">
       <c r="B75" s="32" t="inlineStr">
@@ -1847,14 +1988,30 @@
           <t>Россинский Вадим</t>
         </is>
       </c>
-      <c r="D75" s="34" t="n"/>
-      <c r="E75" s="34" t="n"/>
-      <c r="F75" s="34" t="n"/>
-      <c r="G75" s="34" t="n"/>
-      <c r="H75" s="34" t="n"/>
-      <c r="I75" s="34" t="n"/>
-      <c r="J75" s="34" t="n"/>
-      <c r="K75" s="34" t="n"/>
+      <c r="D75" s="41" t="n">
+        <v>245527</v>
+      </c>
+      <c r="E75" s="41" t="n">
+        <v>343570</v>
+      </c>
+      <c r="F75" s="41" t="n">
+        <v>176445</v>
+      </c>
+      <c r="G75" s="41" t="n">
+        <v>202082</v>
+      </c>
+      <c r="H75" s="41" t="n">
+        <v>424127</v>
+      </c>
+      <c r="I75" s="41" t="n">
+        <v>334011</v>
+      </c>
+      <c r="J75" s="41" t="n">
+        <v>342643</v>
+      </c>
+      <c r="K75" s="41" t="n">
+        <v>334237</v>
+      </c>
     </row>
     <row r="76" ht="12.75" customHeight="1">
       <c r="B76" s="32" t="inlineStr">
@@ -1867,14 +2024,30 @@
           <t>Федосеев Максим</t>
         </is>
       </c>
-      <c r="D76" s="34" t="n"/>
-      <c r="E76" s="34" t="n"/>
-      <c r="F76" s="34" t="n"/>
-      <c r="G76" s="34" t="n"/>
-      <c r="H76" s="34" t="n"/>
-      <c r="I76" s="34" t="n"/>
-      <c r="J76" s="34" t="n"/>
-      <c r="K76" s="34" t="n"/>
+      <c r="D76" s="41" t="n">
+        <v>144032</v>
+      </c>
+      <c r="E76" s="41" t="n">
+        <v>145716</v>
+      </c>
+      <c r="F76" s="41" t="n">
+        <v>92434</v>
+      </c>
+      <c r="G76" s="41" t="n">
+        <v>143686</v>
+      </c>
+      <c r="H76" s="41" t="n">
+        <v>190159</v>
+      </c>
+      <c r="I76" s="41" t="n">
+        <v>220749</v>
+      </c>
+      <c r="J76" s="41" t="n">
+        <v>775616</v>
+      </c>
+      <c r="K76" s="41" t="n">
+        <v>272821</v>
+      </c>
     </row>
     <row r="77" ht="12.75" customHeight="1">
       <c r="B77" s="32" t="inlineStr">
@@ -1887,14 +2060,18 @@
           <t>Фёдорова Анастасия</t>
         </is>
       </c>
-      <c r="D77" s="34" t="n"/>
-      <c r="E77" s="34" t="n"/>
-      <c r="F77" s="34" t="n"/>
-      <c r="G77" s="34" t="n"/>
-      <c r="H77" s="34" t="n"/>
-      <c r="I77" s="34" t="n"/>
-      <c r="J77" s="34" t="n"/>
-      <c r="K77" s="34" t="n"/>
+      <c r="D77" s="41" t="n"/>
+      <c r="E77" s="41" t="n"/>
+      <c r="F77" s="41" t="n"/>
+      <c r="G77" s="41" t="n"/>
+      <c r="H77" s="41" t="n"/>
+      <c r="I77" s="41" t="n"/>
+      <c r="J77" s="41" t="n">
+        <v>100565</v>
+      </c>
+      <c r="K77" s="41" t="n">
+        <v>155451</v>
+      </c>
     </row>
     <row r="78" ht="12.75" customHeight="1">
       <c r="B78" s="19" t="n"/>
@@ -2087,14 +2264,14 @@
           <t>Савинская Евгения</t>
         </is>
       </c>
-      <c r="D91" s="37" t="n"/>
-      <c r="E91" s="37" t="n"/>
-      <c r="F91" s="37" t="n"/>
-      <c r="G91" s="37" t="n"/>
-      <c r="H91" s="37" t="n"/>
-      <c r="I91" s="37" t="n"/>
-      <c r="J91" s="37" t="n"/>
-      <c r="K91" s="37" t="n"/>
+      <c r="D91" s="42" t="n"/>
+      <c r="E91" s="42" t="n"/>
+      <c r="F91" s="42" t="n"/>
+      <c r="G91" s="42" t="n"/>
+      <c r="H91" s="42" t="n"/>
+      <c r="I91" s="42" t="n"/>
+      <c r="J91" s="42" t="n"/>
+      <c r="K91" s="42" t="n"/>
     </row>
     <row r="92" ht="12.75" customHeight="1">
       <c r="B92" s="32" t="inlineStr">
@@ -2107,14 +2284,14 @@
           <t>Багланова Антонина</t>
         </is>
       </c>
-      <c r="D92" s="34" t="n"/>
-      <c r="E92" s="34" t="n"/>
-      <c r="F92" s="34" t="n"/>
-      <c r="G92" s="34" t="n"/>
-      <c r="H92" s="34" t="n"/>
-      <c r="I92" s="34" t="n"/>
-      <c r="J92" s="34" t="n"/>
-      <c r="K92" s="34" t="n"/>
+      <c r="D92" s="42" t="n"/>
+      <c r="E92" s="42" t="n"/>
+      <c r="F92" s="42" t="n"/>
+      <c r="G92" s="42" t="n"/>
+      <c r="H92" s="42" t="n"/>
+      <c r="I92" s="42" t="n"/>
+      <c r="J92" s="42" t="n"/>
+      <c r="K92" s="42" t="n"/>
     </row>
     <row r="93" ht="12.75" customHeight="1">
       <c r="B93" s="32" t="inlineStr">
@@ -2127,14 +2304,14 @@
           <t>Соболев Максим</t>
         </is>
       </c>
-      <c r="D93" s="34" t="n"/>
-      <c r="E93" s="34" t="n"/>
-      <c r="F93" s="34" t="n"/>
-      <c r="G93" s="34" t="n"/>
-      <c r="H93" s="34" t="n"/>
-      <c r="I93" s="34" t="n"/>
-      <c r="J93" s="34" t="n"/>
-      <c r="K93" s="34" t="n"/>
+      <c r="D93" s="42" t="n"/>
+      <c r="E93" s="42" t="n"/>
+      <c r="F93" s="42" t="n"/>
+      <c r="G93" s="42" t="n"/>
+      <c r="H93" s="42" t="n"/>
+      <c r="I93" s="42" t="n"/>
+      <c r="J93" s="42" t="n"/>
+      <c r="K93" s="42" t="n"/>
     </row>
     <row r="94" ht="12.75" customHeight="1">
       <c r="B94" s="32" t="inlineStr">
@@ -2147,14 +2324,14 @@
           <t>Россинский Вадим</t>
         </is>
       </c>
-      <c r="D94" s="34" t="n"/>
-      <c r="E94" s="34" t="n"/>
-      <c r="F94" s="34" t="n"/>
-      <c r="G94" s="34" t="n"/>
-      <c r="H94" s="34" t="n"/>
-      <c r="I94" s="34" t="n"/>
-      <c r="J94" s="34" t="n"/>
-      <c r="K94" s="34" t="n"/>
+      <c r="D94" s="42" t="n"/>
+      <c r="E94" s="42" t="n"/>
+      <c r="F94" s="42" t="n"/>
+      <c r="G94" s="42" t="n"/>
+      <c r="H94" s="42" t="n"/>
+      <c r="I94" s="42" t="n"/>
+      <c r="J94" s="42" t="n"/>
+      <c r="K94" s="42" t="n"/>
     </row>
     <row r="95" ht="12.75" customHeight="1">
       <c r="B95" s="32" t="inlineStr">
@@ -2167,14 +2344,14 @@
           <t>Федосеев Максим</t>
         </is>
       </c>
-      <c r="D95" s="34" t="n"/>
-      <c r="E95" s="34" t="n"/>
-      <c r="F95" s="34" t="n"/>
-      <c r="G95" s="34" t="n"/>
-      <c r="H95" s="34" t="n"/>
-      <c r="I95" s="34" t="n"/>
-      <c r="J95" s="34" t="n"/>
-      <c r="K95" s="34" t="n"/>
+      <c r="D95" s="42" t="n"/>
+      <c r="E95" s="42" t="n"/>
+      <c r="F95" s="42" t="n"/>
+      <c r="G95" s="42" t="n"/>
+      <c r="H95" s="42" t="n"/>
+      <c r="I95" s="42" t="n"/>
+      <c r="J95" s="42" t="n"/>
+      <c r="K95" s="42" t="n"/>
     </row>
     <row r="96" ht="12.75" customHeight="1">
       <c r="B96" s="32" t="inlineStr">
@@ -2187,14 +2364,14 @@
           <t>Фёдорова Анастасия</t>
         </is>
       </c>
-      <c r="D96" s="34" t="n"/>
-      <c r="E96" s="34" t="n"/>
-      <c r="F96" s="34" t="n"/>
-      <c r="G96" s="34" t="n"/>
-      <c r="H96" s="34" t="n"/>
-      <c r="I96" s="34" t="n"/>
-      <c r="J96" s="34" t="n"/>
-      <c r="K96" s="34" t="n"/>
+      <c r="D96" s="42" t="n"/>
+      <c r="E96" s="42" t="n"/>
+      <c r="F96" s="42" t="n"/>
+      <c r="G96" s="42" t="n"/>
+      <c r="H96" s="42" t="n"/>
+      <c r="I96" s="42" t="n"/>
+      <c r="J96" s="42" t="n"/>
+      <c r="K96" s="42" t="n"/>
     </row>
     <row r="97" ht="12.75" customHeight="1">
       <c r="B97" s="19" t="n"/>
